--- a/nr-doc-core-adverse-event/ig/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/nr-doc-core-adverse-event/ig/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:49:16+00:00</t>
+    <t>2026-09-16T12:34:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/nr-doc-core-adverse-event/ig/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:34:54+00:00</t>
+    <t>2026-09-17T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
